--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E55CE4-84DB-4914-8F43-9BB00231EFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F06C0A-8AC7-4F4F-BF88-F8470F6D73EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -172,12 +172,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -542,9 +541,12 @@
       <c r="C5">
         <v>1963</v>
       </c>
+      <c r="D5">
+        <v>1979</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F06C0A-8AC7-4F4F-BF88-F8470F6D73EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8168E356-5FC2-40BE-BCAB-9ACA479E261D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3096" yWindow="2424" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Scioglimento</t>
+  </si>
+  <si>
+    <t>Stella Rossa - Fronte Rivoluzionario Marxista-Leninista</t>
   </si>
 </sst>
 </file>
@@ -195,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}" name="Tabella1" displayName="Tabella1" ref="A1:D16" totalsRowShown="0">
-  <autoFilter ref="A1:D16" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}" name="Tabella1" displayName="Tabella1" ref="A1:D22" totalsRowShown="0">
+  <autoFilter ref="A1:D22" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{DAB1404D-8162-4AF0-9379-D7EB3036E8A9}" name="Nome"/>
     <tableColumn id="2" xr3:uid="{594F3938-7883-4711-A032-B874F009A560}" name="Categoria"/>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.88671875" customWidth="1"/>
@@ -678,6 +681,20 @@
         <v>1969</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1969</v>
+      </c>
+      <c r="D17">
+        <v>1976</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8168E356-5FC2-40BE-BCAB-9ACA479E261D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B302AC-130D-4BF3-B2F9-32F32C375D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3096" yWindow="2424" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Stella Rossa - Fronte Rivoluzionario Marxista-Leninista</t>
+  </si>
+  <si>
+    <t>Savelli</t>
   </si>
 </sst>
 </file>
@@ -473,10 +476,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="1" max="1" width="49.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
   </cols>
@@ -695,6 +699,20 @@
         <v>1976</v>
       </c>
     </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>1963</v>
+      </c>
+      <c r="D18">
+        <v>1982</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B302AC-130D-4BF3-B2F9-32F32C375D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FA5FE2-4CBA-4653-B03F-8DA4426D4468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Savelli</t>
+  </si>
+  <si>
+    <t>Immagine</t>
   </si>
 </sst>
 </file>
@@ -201,13 +204,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}" name="Tabella1" displayName="Tabella1" ref="A1:D22" totalsRowShown="0">
-  <autoFilter ref="A1:D22" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}" name="Tabella1" displayName="Tabella1" ref="A1:E22" totalsRowShown="0">
+  <autoFilter ref="A1:E22" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{DAB1404D-8162-4AF0-9379-D7EB3036E8A9}" name="Nome"/>
     <tableColumn id="2" xr3:uid="{594F3938-7883-4711-A032-B874F009A560}" name="Categoria"/>
     <tableColumn id="3" xr3:uid="{55AFE4C4-903D-4E55-821F-4CB1B7EC4280}" name="Fondazione"/>
     <tableColumn id="4" xr3:uid="{7251D796-81C8-405B-9EC7-27E099F1E6BE}" name="Scioglimento"/>
+    <tableColumn id="5" xr3:uid="{81A23E18-373F-42B1-90C5-87A503DDB09F}" name="Immagine"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -476,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.44140625" customWidth="1"/>
@@ -485,7 +489,7 @@
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -498,8 +502,11 @@
       <c r="D1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -510,7 +517,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -524,7 +531,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -538,7 +545,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -552,7 +559,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -560,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -568,7 +575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -579,7 +586,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -590,7 +597,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -604,7 +611,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -618,7 +625,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -632,7 +639,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -646,7 +653,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -657,7 +664,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -671,7 +678,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FA5FE2-4CBA-4653-B03F-8DA4426D4468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41036772-83A1-47A1-8CA0-407C20D88A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3444" yWindow="2772" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -112,6 +112,18 @@
   </si>
   <si>
     <t>Immagine</t>
+  </si>
+  <si>
+    <t>logo-pcdi.svg</t>
+  </si>
+  <si>
+    <t>logo-UCI.png</t>
+  </si>
+  <si>
+    <t>logo-pcc.svg</t>
+  </si>
+  <si>
+    <t>Unione della gioventù comunista d’Italia (marxista-leninista)</t>
   </si>
 </sst>
 </file>
@@ -480,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.44140625" customWidth="1"/>
@@ -530,6 +542,9 @@
       <c r="D3">
         <v>1991</v>
       </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -544,6 +559,9 @@
       <c r="D4">
         <v>1972</v>
       </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -624,6 +642,9 @@
       <c r="D11">
         <v>1991</v>
       </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -718,6 +739,20 @@
       </c>
       <c r="D18">
         <v>1982</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19">
+        <v>1966</v>
+      </c>
+      <c r="D19">
+        <v>1991</v>
       </c>
     </row>
   </sheetData>

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41036772-83A1-47A1-8CA0-407C20D88A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A92D14-2401-4C36-AA7D-CCA44801DA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3444" yWindow="2772" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,13 +117,13 @@
     <t>logo-pcdi.svg</t>
   </si>
   <si>
-    <t>logo-UCI.png</t>
-  </si>
-  <si>
     <t>logo-pcc.svg</t>
   </si>
   <si>
     <t>Unione della gioventù comunista d’Italia (marxista-leninista)</t>
+  </si>
+  <si>
+    <t>logo-UCI.svg</t>
   </si>
 </sst>
 </file>
@@ -560,7 +560,7 @@
         <v>1972</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -603,6 +603,9 @@
       <c r="C8">
         <v>1921</v>
       </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -642,9 +645,6 @@
       <c r="D11">
         <v>1991</v>
       </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -743,7 +743,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A92D14-2401-4C36-AA7D-CCA44801DA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621C959D-FF0C-4CC4-99B4-58DCFE44F854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>logo-UCI.svg</t>
+  </si>
+  <si>
+    <t>Comitato Centrale del PCC</t>
   </si>
 </sst>
 </file>
@@ -492,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.44140625" customWidth="1"/>
@@ -755,6 +758,17 @@
         <v>1991</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <v>1921</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621C959D-FF0C-4CC4-99B4-58DCFE44F854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC1A78F-29C1-4D81-83D5-7537B32D6663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -51,12 +51,6 @@
     <t>Edizioni Oriente</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Casa discografica</t>
-  </si>
-  <si>
     <t>Centro di Informazione di Verona</t>
   </si>
   <si>
@@ -108,9 +102,6 @@
     <t>Stella Rossa - Fronte Rivoluzionario Marxista-Leninista</t>
   </si>
   <si>
-    <t>Savelli</t>
-  </si>
-  <si>
     <t>Immagine</t>
   </si>
   <si>
@@ -127,6 +118,15 @@
   </si>
   <si>
     <t>Comitato Centrale del PCC</t>
+  </si>
+  <si>
+    <t>Associazione Italia-Cina</t>
+  </si>
+  <si>
+    <t>Associazione di massa</t>
+  </si>
+  <si>
+    <t>201?</t>
   </si>
 </sst>
 </file>
@@ -219,8 +219,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}" name="Tabella1" displayName="Tabella1" ref="A1:E22" totalsRowShown="0">
-  <autoFilter ref="A1:E22" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}" name="Tabella1" displayName="Tabella1" ref="A1:E21" totalsRowShown="0">
+  <autoFilter ref="A1:E21" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{DAB1404D-8162-4AF0-9379-D7EB3036E8A9}" name="Nome"/>
     <tableColumn id="2" xr3:uid="{594F3938-7883-4711-A032-B874F009A560}" name="Categoria"/>
@@ -495,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.44140625" customWidth="1"/>
@@ -512,13 +512,13 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
         <v>25</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -546,7 +546,7 @@
         <v>1991</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -563,7 +563,7 @@
         <v>1972</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -585,65 +585,71 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>1921</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>1921</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>1948</v>
+        <v>1958</v>
+      </c>
+      <c r="D9">
+        <v>1998</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>1958</v>
+        <v>1966</v>
       </c>
       <c r="D10">
-        <v>1998</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="D11">
         <v>1991</v>
@@ -651,52 +657,52 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="D12">
-        <v>1991</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C13">
-        <v>1968</v>
-      </c>
-      <c r="D13">
-        <v>1972</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14">
-        <v>1956</v>
+        <v>1967</v>
+      </c>
+      <c r="D14">
+        <v>1969</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="D15">
         <v>1969</v>
@@ -704,68 +710,54 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D16">
-        <v>1969</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C17">
-        <v>1969</v>
-      </c>
-      <c r="D17">
-        <v>1976</v>
+        <v>1962</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C18">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="D18">
-        <v>1982</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19">
-        <v>1966</v>
-      </c>
-      <c r="D19">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20">
         <v>1921</v>
       </c>
     </row>

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC1A78F-29C1-4D81-83D5-7537B32D6663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B08B6B-9DF5-44B9-85D8-A3908C9E1CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3864" yWindow="1596" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>201?</t>
+  </si>
+  <si>
+    <t>Avanguardia Proletaria Maoista</t>
   </si>
 </sst>
 </file>
@@ -495,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.44140625" customWidth="1"/>
@@ -761,6 +764,20 @@
         <v>1921</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>1968</v>
+      </c>
+      <c r="D20">
+        <v>1969</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B08B6B-9DF5-44B9-85D8-A3908C9E1CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81CD1C6-3031-468B-9EE7-080D146B986D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3864" yWindow="1596" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4212" yWindow="1944" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Avanguardia Proletaria Maoista</t>
+  </si>
+  <si>
+    <t>Partito Comunista (marxista-leninista) Italiano</t>
   </si>
 </sst>
 </file>
@@ -199,11 +202,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -222,8 +226,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}" name="Tabella1" displayName="Tabella1" ref="A1:E21" totalsRowShown="0">
-  <autoFilter ref="A1:E21" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}" name="Tabella1" displayName="Tabella1" ref="A1:E48" totalsRowShown="0">
+  <autoFilter ref="A1:E48" xr:uid="{AF6E7B84-107A-485F-ABC9-02EAAF05F07E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E21">
+    <sortCondition ref="B1:B48"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{DAB1404D-8162-4AF0-9379-D7EB3036E8A9}" name="Nome"/>
     <tableColumn id="2" xr3:uid="{594F3938-7883-4711-A032-B874F009A560}" name="Categoria"/>
@@ -498,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.44140625" customWidth="1"/>
@@ -526,108 +533,99 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C2">
-        <v>1952</v>
+        <v>1962</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1966</v>
-      </c>
-      <c r="D3">
-        <v>1991</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1968</v>
+        <v>1963</v>
       </c>
       <c r="D4">
-        <v>1972</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>1963</v>
-      </c>
-      <c r="D5">
-        <v>1979</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>1958</v>
+      </c>
+      <c r="D6">
+        <v>1998</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>1921</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
+        <v>1964</v>
+      </c>
+      <c r="D7">
+        <v>1991</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8">
-        <v>1948</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9">
-        <v>1958</v>
-      </c>
-      <c r="D9">
-        <v>1998</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -646,60 +644,63 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="D11">
-        <v>1991</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="C12">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="D12">
-        <v>1972</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13">
-        <v>1956</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>16</v>
+      <c r="A14" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="D14">
-        <v>1969</v>
+        <v>1991</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>17</v>
+      <c r="A15" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
@@ -708,73 +709,93 @@
         <v>1968</v>
       </c>
       <c r="D15">
-        <v>1969</v>
+        <v>1972</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16">
-        <v>1969</v>
-      </c>
-      <c r="D16">
-        <v>1976</v>
+        <v>1921</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>1962</v>
-      </c>
-      <c r="D17" t="s">
-        <v>33</v>
+        <v>1968</v>
+      </c>
+      <c r="D17">
+        <v>1969</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="D18">
-        <v>1991</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>1921</v>
+        <v>1968</v>
+      </c>
+      <c r="D19">
+        <v>1969</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20">
-        <v>1968</v>
+        <v>1972</v>
       </c>
       <c r="D20">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21">
+        <v>1967</v>
+      </c>
+      <c r="D21">
         <v>1969</v>
       </c>
     </row>

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81CD1C6-3031-468B-9EE7-080D146B986D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684519C1-BB31-45FF-8136-48F53557B87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4212" yWindow="1944" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>Casa editrice in lingue estere</t>
   </si>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>Partito Comunista (marxista-leninista) Italiano</t>
+  </si>
+  <si>
+    <t>Partito Comunista Unificato d'Italia</t>
+  </si>
+  <si>
+    <t>???</t>
   </si>
 </sst>
 </file>
@@ -202,12 +208,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -505,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.44140625" customWidth="1"/>
@@ -549,7 +554,7 @@
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3">
@@ -682,7 +687,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14" t="s">
@@ -699,7 +704,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" t="s">
         <v>6</v>
       </c>
       <c r="B15" t="s">
@@ -797,6 +802,20 @@
       </c>
       <c r="D21">
         <v>1969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>1977</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/organizzazioni.xlsx
+++ b/data/organizzazioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684519C1-BB31-45FF-8136-48F53557B87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FBFD9B-3AD9-458D-B317-6AFBE8111821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4212" yWindow="1944" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3864" yWindow="1596" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
     <t>Partito Comunista Unificato d'Italia</t>
   </si>
   <si>
-    <t>???</t>
+    <t>????</t>
   </si>
 </sst>
 </file>
@@ -772,8 +772,8 @@
       <c r="C19">
         <v>1968</v>
       </c>
-      <c r="D19">
-        <v>1969</v>
+      <c r="D19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -814,8 +814,8 @@
       <c r="C22">
         <v>1977</v>
       </c>
-      <c r="D22" t="s">
-        <v>37</v>
+      <c r="D22">
+        <v>1984</v>
       </c>
     </row>
   </sheetData>
